--- a/config/metadata.xlsx
+++ b/config/metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Mi unidad\Data Science Projects\Formation\L_Análisis de datos_Futbol - AFECFA\Z_Curso2025-\Dudas Alumnos\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Mi unidad\Data Science Projects\Github\integrador-api-opta\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191F8064-2D6B-40BA-BDD8-1D9F8578EA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415B22F0-F0CB-4BEE-8299-4962FDC4AE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9EB1141D-AC04-4105-A2F1-0C0EA254B4F3}"/>
+    <workbookView xWindow="4428" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{9EB1141D-AC04-4105-A2F1-0C0EA254B4F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -517,10 +517,10 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -543,10 +543,10 @@
         <v>12</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -558,8 +558,8 @@
   </sheetData>
   <autoFilter ref="A1:H2" xr:uid="{4D45D864-13AB-4EE0-A860-5802EA2E8C62}"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{DAC328FE-6B24-469B-AE07-1039697CED73}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{95E20682-FE1E-40E1-8501-B4E00EED2E7B}"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{95E20682-FE1E-40E1-8501-B4E00EED2E7B}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{DAC328FE-6B24-469B-AE07-1039697CED73}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
